--- a/docs/Logic Requirements/Ageipelago Sforza.xlsx
+++ b/docs/Logic Requirements/Ageipelago Sforza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAF4603B-26E9-478A-8EA2-05B7B2EDD340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39B1F4D0-9A52-4FEF-84F0-1A9FC2FA7899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sforza" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="183">
   <si>
     <t>Scenario</t>
   </si>
@@ -168,34 +168,6 @@
 1000 Food
 500 Woos
 750 Gold</t>
-  </si>
-  <si>
-    <r>
-      <t>4 Condottieri
-1 Cavalier
-1 Light Cavalry
-Francesco Sforza
-Misc. Buildings
-Continuos Tribute (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Visconti</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
   </si>
   <si>
     <r>
@@ -2310,15 +2282,6 @@
     <t>Paladin</t>
   </si>
   <si>
-    <t>No Castle Techs
-No Dock Techs
-No Crop Rotation
-University Techs only on Hard Logic
-Chemistry is researched automatically
-On Standard:
-Conscription is researched automatically</t>
-  </si>
-  <si>
     <t>No Spies
 On Standard:
 Light Cavalry and Crossbowman are researched automatically</t>
@@ -2340,6 +2303,77 @@
 Skirmishers, Pikemen, War Galleys, Fire Ships and War Hulks reactive as Counterunits
 Two-Handed Swordsmen, Light Cavalry, Arbalesters and Genoese Crossbowmen as Main Force.
 Bombard Cannons</t>
+  </si>
+  <si>
+    <t>Starting Units</t>
+  </si>
+  <si>
+    <t>Starting Buildings</t>
+  </si>
+  <si>
+    <t>Item-Units</t>
+  </si>
+  <si>
+    <t>Item-Buildings</t>
+  </si>
+  <si>
+    <r>
+      <t>4 Condottieri,1 Cavalier,1 Light Cavalry,Francesco Sforza
+Misc. Buildings
+(Lombardy)
+Continuos Tribute (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Visconti</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Francesco Sforza</t>
+  </si>
+  <si>
+    <t>No Castle Techs
+No Dock Techs
+No Crop Rotation
+University Techs require Monks; only on Hard Logic
+Chemistry is researched automatically
+On Standard:
+Conscription is researched automatically</t>
+  </si>
+  <si>
+    <t>Siege Tower</t>
+  </si>
+  <si>
+    <t>Organ Gun</t>
+  </si>
+  <si>
+    <t>Caravel</t>
+  </si>
+  <si>
+    <t>Capped Ram</t>
+  </si>
+  <si>
+    <t>Galley</t>
+  </si>
+  <si>
+    <t>Scout Cavalry</t>
+  </si>
+  <si>
+    <t>Missionary</t>
   </si>
 </sst>
 </file>
@@ -2515,7 +2549,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -2697,11 +2731,51 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2855,6 +2929,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3240,34 +3329,34 @@
         <v>16</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>23</v>
+        <v>173</v>
       </c>
       <c r="H4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="7" t="s">
         <v>26</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>27</v>
       </c>
       <c r="J4" s="7"/>
       <c r="K4" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L4" s="7"/>
       <c r="M4" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O4" s="7" t="s">
         <v>21</v>
@@ -3280,38 +3369,38 @@
         <v>17</v>
       </c>
       <c r="C5" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="E5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="9" t="s">
+      <c r="I5" s="10" t="s">
         <v>35</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>36</v>
       </c>
       <c r="J5" s="7"/>
       <c r="K5" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="N5" s="7" t="s">
         <v>39</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>40</v>
       </c>
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
@@ -3322,27 +3411,27 @@
         <v>18</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="9" t="s">
-        <v>45</v>
-      </c>
       <c r="G6" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H6" s="9"/>
       <c r="I6" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
@@ -3350,7 +3439,7 @@
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="2:17" ht="357" thickBot="1" x14ac:dyDescent="0.3">
@@ -3358,41 +3447,41 @@
         <v>19</v>
       </c>
       <c r="C7" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>49</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>50</v>
       </c>
       <c r="G7" s="9"/>
       <c r="H7" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="I7" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="I7" s="10" t="s">
-        <v>53</v>
-      </c>
       <c r="J7" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="L7" s="7" t="s">
         <v>61</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>62</v>
       </c>
       <c r="M7" s="7"/>
       <c r="N7" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="2:17" ht="394.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3400,41 +3489,41 @@
         <v>20</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D8" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="H8" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="F8" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>60</v>
-      </c>
       <c r="I8" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="2:17" ht="24" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3467,6 +3556,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
@@ -3474,18 +3564,18 @@
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="47" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C2" s="48"/>
       <c r="D2" s="49"/>
       <c r="G2" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>15</v>
@@ -3493,73 +3583,73 @@
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="50" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C3" s="51"/>
       <c r="D3" s="52"/>
       <c r="G3" s="20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I3" s="17"/>
       <c r="J3" s="17"/>
       <c r="K3" s="33" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I4" s="17"/>
       <c r="J4" s="17"/>
       <c r="K4" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="L4" s="21" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="243.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="L4" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" ht="225" x14ac:dyDescent="0.25">
-      <c r="B5" s="19" t="s">
-        <v>121</v>
-      </c>
       <c r="C5" s="19" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="G5" s="22" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I5" s="17"/>
       <c r="J5" s="17"/>
       <c r="K5" s="25" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L5" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -3567,387 +3657,460 @@
       <c r="C6" s="18"/>
       <c r="D6" s="13"/>
       <c r="G6" s="16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H6" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I6" s="17"/>
       <c r="J6" s="17"/>
       <c r="K6" s="25" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L6" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
       <c r="D7" s="13"/>
       <c r="G7" s="29" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H7" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I7" s="17"/>
       <c r="J7" s="17"/>
       <c r="K7" s="25" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L7" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="13"/>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>172</v>
+      </c>
       <c r="G8" s="24" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H8" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I8" s="17"/>
       <c r="J8" s="17"/>
       <c r="K8" s="25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L8" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="13"/>
+      <c r="B9" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="34"/>
+      <c r="D9" s="54" t="s">
+        <v>124</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>98</v>
+      </c>
       <c r="G9" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H9" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I9" s="17"/>
       <c r="J9" s="17"/>
       <c r="K9" s="25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L9" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="13"/>
+      <c r="B10" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="34"/>
+      <c r="D10" s="54" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>99</v>
+      </c>
       <c r="G10" s="24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H10" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I10" s="17"/>
       <c r="J10" s="17"/>
       <c r="K10" s="25" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L10" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="13"/>
+      <c r="B11" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="34"/>
+      <c r="D11" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>100</v>
+      </c>
       <c r="G11" s="25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H11" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I11" s="17"/>
       <c r="J11" s="17"/>
       <c r="K11" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L11" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="13"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="19" t="s">
+        <v>101</v>
+      </c>
       <c r="G12" s="26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H12" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I12" s="17"/>
       <c r="J12" s="17"/>
       <c r="K12" s="25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L12" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="13"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="19" t="s">
+        <v>97</v>
+      </c>
       <c r="G13" s="26" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H13" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I13" s="17"/>
       <c r="J13" s="17"/>
       <c r="K13" s="25" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L13" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="13"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="19" t="s">
+        <v>110</v>
+      </c>
       <c r="G14" s="26" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H14" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I14" s="17"/>
       <c r="J14" s="17"/>
       <c r="K14" s="25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L14" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="13"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
       <c r="G15" s="26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H15" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I15" s="17"/>
       <c r="J15" s="17"/>
       <c r="K15" s="26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L15" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="13"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
       <c r="G16" s="26" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H16" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I16" s="17"/>
       <c r="J16" s="17"/>
       <c r="K16" s="26" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L16" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
       <c r="G17" s="27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H17" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I17" s="17"/>
       <c r="J17" s="17"/>
       <c r="K17" s="26" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L17" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="34"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
       <c r="G18" s="42" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H18" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I18" s="17"/>
       <c r="J18" s="17"/>
       <c r="K18" s="26" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L18" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
       <c r="G19" s="43" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H19" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I19" s="17"/>
       <c r="J19" s="17"/>
       <c r="K19" s="31" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L19" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="34"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34"/>
       <c r="G20" s="44" t="s">
+        <v>90</v>
+      </c>
+      <c r="H20" s="16" t="s">
         <v>91</v>
-      </c>
-      <c r="H20" s="16" t="s">
-        <v>92</v>
       </c>
       <c r="I20" s="17"/>
       <c r="J20" s="17"/>
       <c r="K20" s="27" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L20" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
       <c r="G21" s="34"/>
       <c r="H21" s="34"/>
       <c r="I21" s="17"/>
       <c r="J21" s="17"/>
       <c r="K21" s="27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L21" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B22" s="34"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
       <c r="G22" s="34"/>
       <c r="H22" s="34"/>
       <c r="I22" s="17"/>
       <c r="J22" s="17"/>
       <c r="K22" s="27" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L22" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B23" s="34"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
       <c r="G23" s="34"/>
       <c r="H23" s="34"/>
       <c r="I23" s="17"/>
       <c r="J23" s="17"/>
       <c r="K23" s="27" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L23" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B24" s="34"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="34"/>
       <c r="G24" s="34"/>
       <c r="H24" s="34"/>
       <c r="I24" s="17"/>
       <c r="J24" s="17"/>
       <c r="K24" s="28" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L24" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="34"/>
       <c r="H25" s="34"/>
       <c r="I25" s="17"/>
       <c r="J25" s="17"/>
       <c r="K25" s="24" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L25" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="34"/>
       <c r="H26" s="34"/>
       <c r="I26" s="17"/>
       <c r="J26" s="17"/>
       <c r="K26" s="24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L26" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="34"/>
       <c r="H27" s="34"/>
       <c r="I27" s="17"/>
       <c r="J27" s="17"/>
       <c r="K27" s="32" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L27" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="34"/>
       <c r="H28" s="34"/>
       <c r="K28" s="30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L28" s="16" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="34"/>
       <c r="H29" s="34"/>
       <c r="K29" s="34"/>
       <c r="L29" s="34"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="34"/>
       <c r="H30" s="34"/>
       <c r="K30" s="34"/>
       <c r="L30" s="34"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="34"/>
       <c r="H31" s="34"/>
       <c r="K31" s="34"/>
       <c r="L31" s="34"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="34"/>
       <c r="H32" s="34"/>
       <c r="K32" s="34"/>
@@ -4029,6 +4192,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
@@ -4036,18 +4200,18 @@
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="47" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C2" s="48"/>
       <c r="D2" s="49"/>
       <c r="G2" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>15</v>
@@ -4055,73 +4219,73 @@
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="50" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C3" s="51"/>
       <c r="D3" s="52"/>
       <c r="G3" s="20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I3" s="17"/>
       <c r="J3" s="17"/>
       <c r="K3" s="36" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G4" s="28" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I4" s="17"/>
       <c r="J4" s="17"/>
       <c r="K4" s="27" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L4" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="75" x14ac:dyDescent="0.25">
       <c r="B5" s="19" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C5" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="D5" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="D5" s="19" t="s">
-        <v>136</v>
-      </c>
       <c r="G5" s="24" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I5" s="17"/>
       <c r="J5" s="17"/>
       <c r="K5" s="27" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L5" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4129,367 +4293,478 @@
       <c r="C6" s="18"/>
       <c r="D6" s="13"/>
       <c r="G6" s="24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I6" s="17"/>
       <c r="J6" s="17"/>
       <c r="K6" s="27" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L6" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
       <c r="D7" s="13"/>
       <c r="G7" s="24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I7" s="17"/>
       <c r="J7" s="17"/>
       <c r="K7" s="27" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L7" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="13"/>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>172</v>
+      </c>
       <c r="G8" s="24" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I8" s="17"/>
       <c r="J8" s="17"/>
       <c r="K8" s="27" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L8" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="13"/>
+      <c r="B9" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="C9" s="55" t="s">
+        <v>98</v>
+      </c>
+      <c r="D9" s="54" t="s">
+        <v>80</v>
+      </c>
+      <c r="E9" s="23" t="s">
+        <v>110</v>
+      </c>
       <c r="G9" s="30" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I9" s="17"/>
       <c r="J9" s="17"/>
       <c r="K9" s="27" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L9" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="13"/>
+      <c r="B10" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="55" t="s">
+        <v>99</v>
+      </c>
+      <c r="D10" s="56" t="s">
+        <v>123</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>105</v>
+      </c>
       <c r="G10" s="31" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H10" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I10" s="17"/>
       <c r="J10" s="17"/>
       <c r="K10" s="27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L10" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="13"/>
+      <c r="B11" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" s="55" t="s">
+        <v>100</v>
+      </c>
+      <c r="D11" s="57" t="s">
+        <v>81</v>
+      </c>
+      <c r="E11" s="54" t="s">
+        <v>111</v>
+      </c>
       <c r="G11" s="35" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H11" s="23" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I11" s="17"/>
       <c r="J11" s="17"/>
       <c r="K11" s="31" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L11" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="13"/>
+      <c r="B12" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" s="55" t="s">
+        <v>101</v>
+      </c>
+      <c r="D12" s="56" t="s">
+        <v>124</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>111</v>
+      </c>
       <c r="G12" s="31" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H12" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I12" s="17"/>
       <c r="J12" s="17"/>
       <c r="K12" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="L12" s="21" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" s="34" t="s">
         <v>97</v>
       </c>
-      <c r="L12" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="13"/>
+      <c r="D13" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="E13" s="54" t="s">
+        <v>110</v>
+      </c>
       <c r="G13" s="35" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H13" s="23" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I13" s="17"/>
       <c r="J13" s="17"/>
       <c r="K13" s="31" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L13" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="13"/>
+      <c r="B14" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="D14" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>114</v>
+      </c>
       <c r="G14" s="15"/>
       <c r="H14" s="15"/>
       <c r="I14" s="17"/>
       <c r="J14" s="17"/>
       <c r="K14" s="31" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L14" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="13"/>
+      <c r="B15" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="C15" s="34"/>
+      <c r="D15" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="E15" s="34"/>
       <c r="G15" s="34"/>
       <c r="H15" s="34"/>
       <c r="I15" s="17"/>
       <c r="J15" s="17"/>
       <c r="K15" s="31" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L15" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="13"/>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="E16" s="34"/>
       <c r="G16" s="34"/>
       <c r="H16" s="34"/>
       <c r="I16" s="17"/>
       <c r="J16" s="17"/>
       <c r="K16" s="31" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L16" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="54" t="s">
+        <v>177</v>
+      </c>
+      <c r="E17" s="34"/>
       <c r="G17" s="34"/>
       <c r="H17" s="34"/>
       <c r="I17" s="17"/>
       <c r="J17" s="17"/>
       <c r="K17" s="31" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L17" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B18" s="34"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" s="34"/>
       <c r="G18" s="34"/>
       <c r="H18" s="34"/>
       <c r="I18" s="17"/>
       <c r="J18" s="17"/>
       <c r="K18" s="31" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L18" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="E19" s="34"/>
       <c r="G19" s="34"/>
       <c r="H19" s="34"/>
       <c r="I19" s="17"/>
       <c r="J19" s="17"/>
       <c r="K19" s="31" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L19" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="34"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="E20" s="34"/>
       <c r="G20" s="34"/>
       <c r="H20" s="34"/>
       <c r="I20" s="17"/>
       <c r="J20" s="17"/>
       <c r="K20" s="31" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L20" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
       <c r="G21" s="34"/>
       <c r="H21" s="34"/>
       <c r="I21" s="17"/>
       <c r="J21" s="17"/>
       <c r="K21" s="31" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L21" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B22" s="34"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
       <c r="G22" s="34"/>
       <c r="H22" s="34"/>
       <c r="I22" s="17"/>
       <c r="J22" s="17"/>
       <c r="K22" s="31" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L22" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B23" s="34"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
       <c r="G23" s="34"/>
       <c r="H23" s="34"/>
       <c r="I23" s="17"/>
       <c r="J23" s="17"/>
       <c r="K23" s="31" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L23" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B24" s="34"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="34"/>
       <c r="G24" s="34"/>
       <c r="H24" s="34"/>
       <c r="I24" s="17"/>
       <c r="J24" s="17"/>
       <c r="K24" s="31" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L24" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="34"/>
       <c r="H25" s="34"/>
       <c r="I25" s="17"/>
       <c r="J25" s="17"/>
       <c r="K25" s="37" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L25" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="34"/>
       <c r="H26" s="34"/>
       <c r="I26" s="17"/>
       <c r="J26" s="17"/>
       <c r="K26" s="37" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L26" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="34"/>
       <c r="H27" s="34"/>
       <c r="I27" s="17"/>
       <c r="J27" s="17"/>
       <c r="K27" s="31" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L27" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="34"/>
       <c r="H28" s="34"/>
       <c r="K28" s="45" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L28" s="16" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="34"/>
       <c r="H29" s="34"/>
       <c r="K29" s="45" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L29" s="16" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="34"/>
       <c r="H30" s="34"/>
       <c r="K30" s="30" t="s">
+        <v>132</v>
+      </c>
+      <c r="L30" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="L30" s="16" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="34"/>
       <c r="H31" s="34"/>
       <c r="K31" s="15"/>
       <c r="L31" s="15"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="34"/>
       <c r="H32" s="34"/>
       <c r="K32" s="34"/>
@@ -4570,7 +4845,7 @@
   <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="2" max="5" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
@@ -4578,18 +4853,18 @@
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="47" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C2" s="48"/>
       <c r="D2" s="49"/>
       <c r="G2" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>15</v>
@@ -4597,73 +4872,73 @@
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="50" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C3" s="51"/>
       <c r="D3" s="52"/>
       <c r="G3" s="20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I3" s="17"/>
       <c r="J3" s="17"/>
       <c r="K3" s="38" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I4" s="17"/>
       <c r="J4" s="17"/>
       <c r="K4" s="31" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L4" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="112.5" x14ac:dyDescent="0.25">
       <c r="B5" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I5" s="17"/>
       <c r="J5" s="17"/>
       <c r="K5" s="31" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L5" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -4671,399 +4946,478 @@
       <c r="C6" s="18"/>
       <c r="D6" s="13"/>
       <c r="G6" s="16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H6" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I6" s="17"/>
       <c r="J6" s="17"/>
       <c r="K6" s="31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L6" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
       <c r="D7" s="13"/>
       <c r="G7" s="41" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H7" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I7" s="17"/>
       <c r="J7" s="17"/>
       <c r="K7" s="31" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L7" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="13"/>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>172</v>
+      </c>
       <c r="G8" s="41" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H8" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I8" s="17"/>
       <c r="J8" s="17"/>
       <c r="K8" s="31" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L8" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="13"/>
+      <c r="B9" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
       <c r="G9" s="31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H9" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I9" s="17"/>
       <c r="J9" s="17"/>
       <c r="K9" s="31" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L9" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="13"/>
+      <c r="B10" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
       <c r="G10" s="31" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H10" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I10" s="17"/>
       <c r="J10" s="17"/>
       <c r="K10" s="31" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L10" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="13"/>
+      <c r="B11" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
       <c r="G11" s="31" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H11" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I11" s="17"/>
       <c r="J11" s="17"/>
       <c r="K11" s="31" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L11" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="13"/>
+      <c r="B12" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
       <c r="G12" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H12" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I12" s="17"/>
       <c r="J12" s="17"/>
       <c r="K12" s="31" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L12" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="13"/>
+      <c r="B13" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
       <c r="G13" s="31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H13" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I13" s="17"/>
       <c r="J13" s="17"/>
       <c r="K13" s="31" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L13" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="13"/>
+      <c r="B14" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
       <c r="G14" s="31" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H14" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I14" s="17"/>
       <c r="J14" s="17"/>
       <c r="K14" s="31" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L14" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="13"/>
+      <c r="B15" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
       <c r="G15" s="31" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H15" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I15" s="17"/>
       <c r="J15" s="17"/>
       <c r="K15" s="31" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L15" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="13"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
       <c r="G16" s="31" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H16" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I16" s="17"/>
       <c r="J16" s="17"/>
       <c r="K16" s="31" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L16" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
       <c r="G17" s="31" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H17" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I17" s="17"/>
       <c r="J17" s="17"/>
       <c r="K17" s="31" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L17" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="34"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
       <c r="G18" s="31" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H18" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I18" s="17"/>
       <c r="J18" s="17"/>
       <c r="K18" s="31" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L18" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
       <c r="G19" s="31" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H19" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I19" s="17"/>
       <c r="J19" s="17"/>
       <c r="K19" s="31" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L19" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="34"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34"/>
       <c r="G20" s="31" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H20" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I20" s="17"/>
       <c r="J20" s="17"/>
       <c r="K20" s="31" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L20" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
       <c r="G21" s="31" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H21" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I21" s="17"/>
       <c r="J21" s="17"/>
       <c r="K21" s="31" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L21" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B22" s="34"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
       <c r="G22" s="31" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H22" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I22" s="17"/>
       <c r="J22" s="17"/>
       <c r="K22" s="31" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L22" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B23" s="34"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
       <c r="G23" s="35" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H23" s="23" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I23" s="17"/>
       <c r="J23" s="17"/>
       <c r="K23" s="31" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L23" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B24" s="34"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="34"/>
       <c r="G24" s="15"/>
       <c r="H24" s="15"/>
       <c r="I24" s="17"/>
       <c r="J24" s="17"/>
       <c r="K24" s="31" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L24" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="34"/>
       <c r="H25" s="34"/>
       <c r="I25" s="17"/>
       <c r="J25" s="17"/>
       <c r="K25" s="37" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L25" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="34"/>
       <c r="H26" s="34"/>
       <c r="I26" s="17"/>
       <c r="J26" s="17"/>
       <c r="K26" s="37" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L26" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="34"/>
       <c r="H27" s="34"/>
       <c r="I27" s="17"/>
       <c r="J27" s="17"/>
       <c r="K27" s="31" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L27" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="34"/>
       <c r="H28" s="34"/>
       <c r="K28" s="35" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L28" s="23" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="34"/>
       <c r="H29" s="34"/>
       <c r="K29" s="15"/>
       <c r="L29" s="15"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="34"/>
       <c r="H30" s="34"/>
       <c r="K30" s="34"/>
       <c r="L30" s="34"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="34"/>
       <c r="H31" s="34"/>
       <c r="K31" s="34"/>
       <c r="L31" s="34"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="34"/>
       <c r="H32" s="34"/>
       <c r="K32" s="34"/>
@@ -5145,6 +5499,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
@@ -5152,18 +5507,18 @@
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="47" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C2" s="48"/>
       <c r="D2" s="49"/>
       <c r="G2" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>15</v>
@@ -5171,73 +5526,73 @@
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="50" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C3" s="51"/>
       <c r="D3" s="52"/>
       <c r="G3" s="20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I3" s="17"/>
       <c r="J3" s="17"/>
       <c r="K3" s="36" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I4" s="17"/>
       <c r="J4" s="17"/>
       <c r="K4" s="30" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L4" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B5" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D5" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="G5" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="G5" s="16" t="s">
-        <v>149</v>
-      </c>
       <c r="H5" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I5" s="17"/>
       <c r="J5" s="17"/>
       <c r="K5" s="30" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L5" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -5245,403 +5600,480 @@
       <c r="C6" s="18"/>
       <c r="D6" s="13"/>
       <c r="G6" s="30" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H6" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I6" s="17"/>
       <c r="J6" s="17"/>
       <c r="K6" s="30" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L6" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
       <c r="D7" s="13"/>
       <c r="G7" s="44" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H7" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I7" s="17"/>
       <c r="J7" s="17"/>
       <c r="K7" s="30" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L7" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="13"/>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>172</v>
+      </c>
       <c r="G8" s="30" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H8" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I8" s="17"/>
       <c r="J8" s="17"/>
       <c r="K8" s="30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L8" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="13"/>
+      <c r="B9" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="C9" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="D9" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="E9" s="54" t="s">
+        <v>129</v>
+      </c>
       <c r="G9" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H9" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I9" s="17"/>
       <c r="J9" s="17"/>
       <c r="K9" s="30" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L9" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="13"/>
+      <c r="B10" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="E10" s="54" t="s">
+        <v>101</v>
+      </c>
       <c r="G10" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H10" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I10" s="17"/>
       <c r="J10" s="17"/>
       <c r="K10" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L10" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="13"/>
+      <c r="B11" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="D11" s="34"/>
+      <c r="E11" s="54" t="s">
+        <v>111</v>
+      </c>
       <c r="G11" s="30" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H11" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I11" s="17"/>
       <c r="J11" s="17"/>
       <c r="K11" s="30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L11" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="13"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="54" t="s">
+        <v>104</v>
+      </c>
       <c r="G12" s="30" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H12" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I12" s="17"/>
       <c r="J12" s="17"/>
       <c r="K12" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L12" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="13"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="54" t="s">
+        <v>145</v>
+      </c>
       <c r="G13" s="30" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H13" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I13" s="17"/>
       <c r="J13" s="17"/>
       <c r="K13" s="30" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L13" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="13"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="19" t="s">
+        <v>103</v>
+      </c>
       <c r="G14" s="30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H14" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I14" s="17"/>
       <c r="J14" s="17"/>
       <c r="K14" s="30" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L14" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="13"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
       <c r="G15" s="30" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H15" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I15" s="17"/>
       <c r="J15" s="17"/>
       <c r="K15" s="30" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L15" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="13"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
       <c r="G16" s="30" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H16" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I16" s="17"/>
       <c r="J16" s="17"/>
       <c r="K16" s="30" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L16" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
       <c r="G17" s="30" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H17" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I17" s="17"/>
       <c r="J17" s="17"/>
       <c r="K17" s="30" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L17" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="18" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B18" s="34"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
       <c r="G18" s="30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H18" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I18" s="17"/>
       <c r="J18" s="17"/>
       <c r="K18" s="30" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L18" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
       <c r="G19" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H19" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I19" s="17"/>
       <c r="J19" s="17"/>
       <c r="K19" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L19" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="20" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B20" s="34"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34"/>
       <c r="G20" s="30" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H20" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I20" s="17"/>
       <c r="J20" s="17"/>
       <c r="K20" s="30" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L20" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
       <c r="G21" s="30" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H21" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I21" s="17"/>
       <c r="J21" s="17"/>
       <c r="K21" s="30" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L21" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B22" s="34"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
       <c r="G22" s="25" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H22" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I22" s="17"/>
       <c r="J22" s="17"/>
       <c r="K22" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L22" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B23" s="34"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
       <c r="G23" s="25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H23" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I23" s="17"/>
       <c r="J23" s="17"/>
       <c r="K23" s="39" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L23" s="23" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B24" s="34"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="34"/>
       <c r="G24" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H24" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I24" s="17"/>
       <c r="J24" s="17"/>
       <c r="K24" s="15"/>
       <c r="L24" s="15"/>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="24" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H25" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I25" s="17"/>
       <c r="J25" s="17"/>
       <c r="K25" s="34"/>
       <c r="L25" s="34"/>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="29" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H26" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I26" s="17"/>
       <c r="J26" s="17"/>
       <c r="K26" s="34"/>
       <c r="L26" s="34"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="46" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H27" s="23" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I27" s="17"/>
       <c r="J27" s="17"/>
       <c r="K27" s="34"/>
       <c r="L27" s="34"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="24" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H28" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K28" s="34"/>
       <c r="L28" s="34"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="24" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K29" s="34"/>
       <c r="L29" s="34"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="34"/>
       <c r="H30" s="34"/>
       <c r="K30" s="34"/>
       <c r="L30" s="34"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="34"/>
       <c r="H31" s="34"/>
       <c r="K31" s="34"/>
       <c r="L31" s="34"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="34"/>
       <c r="H32" s="34"/>
       <c r="K32" s="34"/>
@@ -5722,7 +6154,7 @@
   <dimension ref="B1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="2" max="5" width="22.5703125" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
@@ -5730,18 +6162,18 @@
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="47" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C2" s="48"/>
       <c r="D2" s="49"/>
       <c r="G2" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>15</v>
@@ -5749,73 +6181,73 @@
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="50" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C3" s="51"/>
       <c r="D3" s="52"/>
       <c r="G3" s="20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I3" s="17"/>
       <c r="J3" s="17"/>
       <c r="K3" s="38" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I4" s="17"/>
       <c r="J4" s="17"/>
       <c r="K4" s="31" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L4" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B5" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I5" s="17"/>
       <c r="J5" s="17"/>
       <c r="K5" s="31" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L5" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -5823,407 +6255,480 @@
       <c r="C6" s="18"/>
       <c r="D6" s="13"/>
       <c r="G6" s="16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H6" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I6" s="17"/>
       <c r="J6" s="17"/>
       <c r="K6" s="31" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L6" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
       <c r="D7" s="13"/>
       <c r="G7" s="16" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H7" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I7" s="17"/>
       <c r="J7" s="17"/>
       <c r="K7" s="31" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L7" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="13"/>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>172</v>
+      </c>
       <c r="G8" s="30" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H8" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I8" s="17"/>
       <c r="J8" s="17"/>
       <c r="K8" s="31" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L8" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="13"/>
+      <c r="B9" s="53" t="s">
+        <v>174</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="D9" s="34"/>
+      <c r="E9" s="54" t="s">
+        <v>114</v>
+      </c>
       <c r="G9" s="30" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H9" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I9" s="17"/>
       <c r="J9" s="17"/>
       <c r="K9" s="31" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L9" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="13"/>
+      <c r="B10" s="56" t="s">
+        <v>124</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" s="34"/>
+      <c r="E10" s="54" t="s">
+        <v>110</v>
+      </c>
       <c r="G10" s="30" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H10" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I10" s="17"/>
       <c r="J10" s="17"/>
       <c r="K10" s="31" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L10" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="13"/>
+      <c r="B11" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="54" t="s">
+        <v>105</v>
+      </c>
       <c r="G11" s="30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H11" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I11" s="17"/>
       <c r="J11" s="17"/>
       <c r="K11" s="31" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L11" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="13"/>
+      <c r="B12" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="54" t="s">
+        <v>100</v>
+      </c>
       <c r="G12" s="30" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H12" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I12" s="17"/>
       <c r="J12" s="17"/>
       <c r="K12" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="L12" s="21" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="54" t="s">
         <v>99</v>
       </c>
-      <c r="L12" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="13"/>
       <c r="G13" s="44" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H13" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I13" s="17"/>
       <c r="J13" s="17"/>
       <c r="K13" s="31" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L13" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="13"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="19" t="s">
+        <v>101</v>
+      </c>
       <c r="G14" s="31" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H14" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I14" s="17"/>
       <c r="J14" s="17"/>
       <c r="K14" s="31" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L14" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="13"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
       <c r="G15" s="31" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H15" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I15" s="17"/>
       <c r="J15" s="17"/>
       <c r="K15" s="31" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L15" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="13"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
       <c r="G16" s="31" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H16" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I16" s="17"/>
       <c r="J16" s="17"/>
       <c r="K16" s="31" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L16" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
       <c r="G17" s="31" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H17" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I17" s="17"/>
       <c r="J17" s="17"/>
       <c r="K17" s="31" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L17" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="34"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
       <c r="G18" s="31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H18" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I18" s="17"/>
       <c r="J18" s="17"/>
       <c r="K18" s="31" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L18" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
       <c r="G19" s="31" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H19" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I19" s="17"/>
       <c r="J19" s="17"/>
       <c r="K19" s="31" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L19" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="34"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34"/>
       <c r="G20" s="31" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H20" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I20" s="17"/>
       <c r="J20" s="17"/>
       <c r="K20" s="31" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L20" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
       <c r="G21" s="31" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H21" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I21" s="17"/>
       <c r="J21" s="17"/>
       <c r="K21" s="31" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L21" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="22" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B22" s="34"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
       <c r="G22" s="31" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H22" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I22" s="17"/>
       <c r="J22" s="17"/>
       <c r="K22" s="31" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L22" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B23" s="34"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
       <c r="G23" s="24" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H23" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I23" s="17"/>
       <c r="J23" s="17"/>
       <c r="K23" s="31" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L23" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B24" s="34"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="34"/>
       <c r="G24" s="24" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H24" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I24" s="17"/>
       <c r="J24" s="17"/>
       <c r="K24" s="37" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L24" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="25" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G25" s="45" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I25" s="17"/>
       <c r="J25" s="17"/>
       <c r="K25" s="29" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L25" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G26" s="34"/>
       <c r="H26" s="34"/>
       <c r="I26" s="17"/>
       <c r="J26" s="17"/>
       <c r="K26" s="24" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L26" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G27" s="34"/>
       <c r="H27" s="34"/>
       <c r="I27" s="17"/>
       <c r="J27" s="17"/>
       <c r="K27" s="24" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L27" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="34"/>
       <c r="H28" s="34"/>
       <c r="K28" s="39" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L28" s="23" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="34"/>
       <c r="H29" s="34"/>
       <c r="K29" s="40"/>
       <c r="L29" s="15"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="34"/>
       <c r="H30" s="34"/>
       <c r="K30" s="34"/>
       <c r="L30" s="34"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="34"/>
       <c r="H31" s="34"/>
       <c r="K31" s="34"/>
       <c r="L31" s="34"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="34"/>
       <c r="H32" s="34"/>
       <c r="K32" s="34"/>
